--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564991818</v>
+        <v>46157.93087259668</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93087259668</v>
+        <v>46157.93165549789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93165549789</v>
+        <v>46157.93396958323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396958323</v>
+        <v>46157.93714591795</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93714591795</v>
+        <v>46158.28213399479</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213399479</v>
+        <v>46158.29674666081</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674666081</v>
+        <v>46158.29811323129</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811323129</v>
+        <v>46158.33384260266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384260266</v>
+        <v>46158.36853405735</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36853405735</v>
+        <v>46158.37284394167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
